--- a/EXTRA/test_features_ver1.xlsx
+++ b/EXTRA/test_features_ver1.xlsx
@@ -1,26 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIN-LOR\Documents\LTM_CARO\Project\EXTRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uteduvn-my.sharepoint.com/personal/phucht3420_ut_edu_vn/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C376D6EE-8146-4C8F-BD8A-21BA9E216048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{E6717CCB-798E-47D7-8C2B-C4283F2D882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B27E51BE-EBBC-434F-A1E5-7413AE26B370}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Core Features Tests" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="8">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="8">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>No</t>
   </si>
@@ -46,13 +154,20 @@
     <t>Kiểm tra tính năng kết nối mạng của người chơi từ ứng dụng Client tới Server thông qua cổng Socket IP &amp; Port.</t>
   </si>
   <si>
+    <t>Nhập Server IP: 127.0.0.1, Tên người chơi.</t>
+  </si>
+  <si>
+    <t>TCP Socket kết nối thành công.
+Server log ghi nhận địa chỉ IP Client vừa kết nối.</t>
+  </si>
+  <si>
     <t>Client gửi yêu cầu thách đấu</t>
   </si>
   <si>
     <t>Người chơi gửi lời mời thách đấu tới một người chơi khác đang trực tuyến trong phòng sảnh chờ.</t>
   </si>
   <si>
-    <t>Tại danh sách online ở sảnh chờ, click chọn 'AI_Minimax_Bot'.
+    <t>Tại danh sách online ở sảnh chờ, click chọn Tên Người Chơi.
 Nhấn nút 'GỬI LỜI THÁCH ĐẤU'.</t>
   </si>
   <si>
@@ -60,29 +175,17 @@
 Đối thủ nhận được thông báo mời thách đấu và đồng ý vào trận.</t>
   </si>
   <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[Thách đấu] Người chơi 'NguoiChoi_A' đã thách đấu 'AI_Minimax_Bot' (Mã thách đấu: a1b2c3d4)
-[Thách đấu] 'AI_Minimax_Bot' đã chấp nhận thách đấu. Khởi tạo phòng chơi...</t>
-  </si>
-  <si>
     <t>Server lưu lại lịch sử đấu</t>
   </si>
   <si>
     <t>Sau khi trận đấu kết thúc (do có người chơi thắng cuộc, hết giờ lượt đi, hoặc thoát trận), Server tự động lưu trữ thông tin lịch sử đấu vào cơ sở dữ liệu PostgreSQL.</t>
   </si>
   <si>
-    <t>Một trận đấu kết thúc (đạt 5 quân liên tiếp, hoặc hết 300s đếm ngược).
+    <t>Một trận đấu kết thúc (đạt 5 quân liên tiếp, hoặc hết thời gian đếm ngược).
 Server tự động gọi luồng SaveMatchHistoryAsync.</t>
   </si>
   <si>
     <t>Bản ghi trận đấu gồm: ID trận, tên 2 người chơi, người thắng, chế độ chơi, thời gian chơi, chuỗi nước đi được ghi nhận thành công vào bảng match_histories trong DB.</t>
-  </si>
-  <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[Trận đấu - Phòng cờ] Trận đấu kết thúc! 'NguoiChoi_A' chiến thắng do đạt đủ 5 quân liên tiếp.
-[Database] Đã lưu lịch sử đấu cho trận: 7a8b9c0d-e1f2-3a4b-5c6d-7e8f9a0b1c2d</t>
   </si>
   <si>
     <t>Có count đếm thời gian cho mỗi client</t>
@@ -98,12 +201,6 @@
 Nếu đồng hồ đếm ngược về 0, Server tự động xử thua người chơi đó và kết thúc trận đấu.</t>
   </si>
   <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[Test] Đồng hồ đếm ngược lượt đi hoạt động chính xác.
-[Trận đấu - Phòng cờ] Hết giờ! Người chơi 'AI_Minimax_Bot' đã thua cuộc. Người chơi 'NguoiChoi_A' thắng cuộc!</t>
-  </si>
-  <si>
     <t>Chat giữa 2 người chơi</t>
   </si>
   <si>
@@ -118,12 +215,6 @@
 Nội dung chat hiển thị ngay lập tức trong hộp thoại chat của cả hai người chơi.</t>
   </si>
   <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[Chat] Người chơi 'NguoiChoi_A' gửi tin nhắn: 'Chào bạn, chúc chơi vui!'
-[Chat] Đối thủ 'AI_Minimax_Bot' nhận tin nhắn thành công.</t>
-  </si>
-  <si>
     <t>Xem lại trận đấu</t>
   </si>
   <si>
@@ -138,10 +229,7 @@
 Cho phép nhấp chuột để đi từng nước cờ tuần tự từ đầu đến cuối dựa trên chuỗi tọa độ lưu trữ (MovesData).</t>
   </si>
   <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[Replay] Khởi tạo bàn cờ xem lại trận đấu cho người chơi 'NguoiChoi_A'.
-[Replay] Đọc chuỗi nước đi thành công: 'Player1:7,7;Player2:8,8;Player1:7,8;Player2:8,9;Player1:7,9...'</t>
+    <t>Chơi với AI</t>
   </si>
   <si>
     <t>Người chơi gửi thách đấu và đánh cờ trực tiếp với Bot AI sử dụng thuật toán Minimax tính toán nước đi.</t>
@@ -153,28 +241,23 @@
     <t>Bot AI tự động tính toán điểm số bàn cờ bằng thuật toán Minimax và tự động gửi gói tin phản hồi nước đi tối ưu lên Server sau vài mili-giây.</t>
   </si>
   <si>
-    <t>PASSED
-[LOG MINH CHỨNG]:
-[AI Engine] Bot 'AI_Minimax_Bot' đang tính toán nước đi tối ưu...
-[AI Engine] Nước đi tính toán của AI: X=8, Y=8 (Score: 1200)
-[AI Engine] Gửi nước đi thành công lên Server.</t>
-  </si>
-  <si>
-    <t>Chơi với AI</t>
-  </si>
-  <si>
-    <t>TCP Socket kết nối thành công.
-Server log ghi nhận địa chỉ IP Client vừa kết nối.</t>
-  </si>
-  <si>
-    <t>Nhập Server IP: 127.0.0.1, Tên người chơi.</t>
+    <t>Bảng Xếp Hạng</t>
+  </si>
+  <si>
+    <t>Người chơi xem những người có thứ hạng cao</t>
+  </si>
+  <si>
+    <t>Tại sảnh chờ, bấm Ranking.</t>
+  </si>
+  <si>
+    <t>Hiện bảng xếp theo tứ thứ tự điểm số</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,14 +267,29 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -236,16 +334,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -253,26 +351,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -288,6 +394,105 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -575,18 +780,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="72" customWidth="1"/>
+    <col min="1" max="1" width="6" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46" style="2" customWidth="1"/>
+    <col min="4" max="4" width="38" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44" style="2" customWidth="1"/>
+    <col min="6" max="6" width="72" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,145 +812,168 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+    <row r="3" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="5" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="5" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="5" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="139.9" customHeight="1">
+      <c r="A9" s="8">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>36</v>
+      <c r="F9" s="10" t="e" vm="8">
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EXTRA/test_features_ver1.xlsx
+++ b/EXTRA/test_features_ver1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uteduvn-my.sharepoint.com/personal/phucht3420_ut_edu_vn/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIN-LOR\Documents\LTM_CARO\Project\EXTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{E6717CCB-798E-47D7-8C2B-C4283F2D882D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B27E51BE-EBBC-434F-A1E5-7413AE26B370}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6EAA43-C02C-41F2-BD4D-0F27F2579AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -257,7 +257,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -781,7 +781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
     <col min="2" max="2" width="32" style="2" customWidth="1"/>
@@ -789,10 +789,10 @@
     <col min="4" max="4" width="38" style="2" customWidth="1"/>
     <col min="5" max="5" width="44" style="2" customWidth="1"/>
     <col min="6" max="6" width="72" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="2"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="139.9" customHeight="1">
+    <row r="2" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -832,7 +832,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="139.9" customHeight="1">
+    <row r="3" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -852,7 +852,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="139.9" customHeight="1">
+    <row r="4" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -872,7 +872,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="139.9" customHeight="1">
+    <row r="5" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -892,7 +892,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="139.9" customHeight="1">
+    <row r="6" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -912,7 +912,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="139.9" customHeight="1">
+    <row r="7" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -932,7 +932,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="139.9" customHeight="1">
+    <row r="8" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -952,7 +952,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="139.9" customHeight="1">
+    <row r="9" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>9</v>
       </c>

--- a/EXTRA/test_features_ver1.xlsx
+++ b/EXTRA/test_features_ver1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIN-LOR\Documents\LTM_CARO\Project\EXTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6EAA43-C02C-41F2-BD4D-0F27F2579AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1268D4-5638-4599-823A-D59DD5B6AA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,100 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="8">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="8">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-    <bk>
-      <rc t="1" v="6"/>
-    </bk>
-    <bk>
-      <rc t="1" v="7"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>No</t>
   </si>
@@ -251,6 +159,30 @@
   </si>
   <si>
     <t>Hiện bảng xếp theo tứ thứ tự điểm số</t>
+  </si>
+  <si>
+    <t>Imagine/Client_Server</t>
+  </si>
+  <si>
+    <t>Imagine/Challenge</t>
+  </si>
+  <si>
+    <t>Imagine/His</t>
+  </si>
+  <si>
+    <t>Imagine/Time</t>
+  </si>
+  <si>
+    <t>Imagine/chat</t>
+  </si>
+  <si>
+    <t>Imagine/WatchHis</t>
+  </si>
+  <si>
+    <t>Imagine/PlayAI</t>
+  </si>
+  <si>
+    <t>Imagine/BangXepHang</t>
   </si>
 </sst>
 </file>
@@ -351,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -378,7 +310,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,105 +325,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>4</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>5</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>6</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>7</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-  <rel r:id="rId5"/>
-  <rel r:id="rId6"/>
-  <rel r:id="rId7"/>
-  <rel r:id="rId8"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -828,8 +660,8 @@
       <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="F2" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -848,8 +680,8 @@
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="e" vm="2">
-        <v>#VALUE!</v>
+      <c r="F3" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -868,8 +700,8 @@
       <c r="E4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="5" t="e" vm="3">
-        <v>#VALUE!</v>
+      <c r="F4" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -888,8 +720,8 @@
       <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="5" t="e" vm="4">
-        <v>#VALUE!</v>
+      <c r="F5" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -908,8 +740,8 @@
       <c r="E6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="5" t="e" vm="5">
-        <v>#VALUE!</v>
+      <c r="F6" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -928,8 +760,8 @@
       <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="5" t="e" vm="6">
-        <v>#VALUE!</v>
+      <c r="F7" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -948,13 +780,13 @@
       <c r="E8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="5" t="e" vm="7">
-        <v>#VALUE!</v>
+      <c r="F8" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="139.94999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>34</v>
@@ -968,8 +800,8 @@
       <c r="E9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="10" t="e" vm="8">
-        <v>#VALUE!</v>
+      <c r="F9" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/EXTRA/test_features_ver1.xlsx
+++ b/EXTRA/test_features_ver1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WIN-LOR\Documents\LTM_CARO\Project\EXTRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1268D4-5638-4599-823A-D59DD5B6AA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF4A92BE-9F04-44C8-98DD-74EBC4CA34B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
